--- a/Таблицы/Шаблон_замера_локализации.xlsx
+++ b/Таблицы/Шаблон_замера_локализации.xlsx
@@ -18,8 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0 ₽"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,11 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +62,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -103,6 +123,42 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1162,7 +1218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1225,409 +1281,2280 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n"/>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Клевер»</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>750</v>
+      </c>
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n"/>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>D274</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Листики»</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>420</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>D249</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Капли»</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>330</v>
+      </c>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>D354</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Ракушки»</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>MSHK-039</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Найтли»</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="8" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>MSH-074</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Эстелла»</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>270</v>
+      </c>
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>D159</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Скарабеи»</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="G10" s="8" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>MSHK-037</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Габриэль»</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="G11" s="8" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>D531</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Доминика»</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="G12" s="8" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>MSHK-028</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Колье «Алма»</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>D388</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Листва»</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G14" s="8" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>D542</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Кольцо «Анемон»</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G15" s="8" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>D355</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Рыбки»</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G16" s="8" t="inlineStr"/>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>MSH-082</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Сабрина»</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G17" s="8" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>D512</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Афина»</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G18" s="8" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>MSHK-045</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Зои»</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>D535</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Камилла»</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G20" s="8" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>MSH-073</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Матильда»</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G21" s="8" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>MSH-083</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Сабрина»</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G22" s="8" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>D529</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Кольцо «Ирис»</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G23" s="8" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>D519</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Весенние тюльпаны»</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G24" s="8" t="inlineStr"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Цикада»</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G25" s="8" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>MSH-007</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Исидора»</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>D364</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Кэрри»</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>D528</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Кольцо «Ирис»</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="G28" s="8" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>D495</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Кольцо «Роза»</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>D513</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Афина»</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="G30" s="8" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>MSHK-055</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Эмма»</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="G31" s="8" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>D216</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Колибри»</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G32" s="8" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>MSH-002</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Египетские скарабеи»</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n"/>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>D527</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Кольцо «Ирис»</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G34" s="8" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n"/>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>MSH-096</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Валерия»</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n"/>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>MSH-078</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Жанин»</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G36" s="8" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>MSH-013</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Лучиана»</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n"/>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>MSH-026</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Алисия»</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G38" s="8" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n"/>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>D518</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Тропики»</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G39" s="8" t="inlineStr"/>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n"/>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>D292</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Винтаж»</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G40" s="8" t="inlineStr"/>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n"/>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>D117</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Сережки ассиметричные «Змеи»</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G41" s="8" t="inlineStr"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n"/>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>MSH-065</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Агнес»</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G42" s="8" t="inlineStr"/>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n"/>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>MSHK-029</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Колье «Счастливое число 7»</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="G43" s="8" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>D360</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Звездочки»</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="G44" s="8" t="inlineStr"/>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Ставки забора: WB 230 ₽/шт, Ozon 30 ₽/шт (товар возвращается для перепродажи)</t>
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>D507-S</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Сережки ассиметричные «Змеи»</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>D523</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «День и ночь»</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="G46" s="8" t="inlineStr"/>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>D491</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Катарина»</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="G47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>MSH-094</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Лора»</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="G48" s="8" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>MSH-097</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Тайна сердца»</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>MSHK-039</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Найтли»</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr"/>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>MSH-072</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Барбара»</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="12" t="inlineStr"/>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>MSH-013</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Лучиана»</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="12" t="inlineStr"/>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>MSH-073</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Матильда»</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="12" t="inlineStr"/>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>MSH-065</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Агнес»</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F54" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="12" t="inlineStr"/>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>MSH-025</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Лаура»</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="12" t="inlineStr"/>
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>D175DSR035</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Клевер»</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="12" t="inlineStr"/>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>MSH-012</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Лучиана»</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="12" t="inlineStr"/>
+      <c r="H57" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>D513</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Афина»</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="12" t="inlineStr"/>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>D175DSR098</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Нежный клевер»</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="12" t="inlineStr"/>
+      <c r="H59" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>MSHK-037</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Габриэль»</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="12" t="inlineStr"/>
+      <c r="H60" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>MSHK-036</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Сильвия»</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="12" t="inlineStr"/>
+      <c r="H61" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>MSH-074</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Эстелла»</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="12" t="inlineStr"/>
+      <c r="H62" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>MSH-070</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Марго»</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="12" t="inlineStr"/>
+      <c r="H63" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>D175DSR034</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Клевер»</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="12" t="inlineStr"/>
+      <c r="H64" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>MSH-014</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Азалия»</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="12" t="inlineStr"/>
+      <c r="H65" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>D193DSR047</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Ника»</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="12" t="inlineStr"/>
+      <c r="H66" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="inlineStr">
+        <is>
+          <t>D114DSMR034</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>Моносережка «Перо»</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" s="17" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G67" s="15" t="inlineStr"/>
+      <c r="H67" s="15" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>D493</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>Сережки «Глаза»</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F68" s="17" t="n">
+        <v>920</v>
+      </c>
+      <c r="G68" s="15" t="inlineStr"/>
+      <c r="H68" s="15" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="15" t="inlineStr">
+        <is>
+          <t>D202DSR069-S</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>Сережки «Змеи»</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" s="17" t="n">
+        <v>920</v>
+      </c>
+      <c r="G69" s="15" t="inlineStr"/>
+      <c r="H69" s="15" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="18">
+        <f>SUM(E4:E69)</f>
+        <v/>
+      </c>
+      <c r="F71" s="19">
+        <f>SUM(F4:F69)</f>
+        <v/>
+      </c>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Ставки: WB 230 ₽/шт, Ozon 30 ₽/шт (товар возвращается для перепродажи). Распродажа/списание — забор 0 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Оранжевый — Ozon забрать (мёртвый неликвид) · Зелёный — WB распродать · Жёлтый — WB забрать (дорогой L1).</t>
         </is>
       </c>
     </row>

--- a/Таблицы/Шаблон_замера_локализации.xlsx
+++ b/Таблицы/Шаблон_замера_локализации.xlsx
@@ -1218,23 +1218,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Реестр забора / распродажи неликвида</t>
+          <t>Реестр забора / распродажи неликвида (мёртвый складской остаток)</t>
         </is>
       </c>
     </row>
@@ -1251,710 +1253,920 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Размер</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>Площадка</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Действие</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Кол-во, шт</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Стоимость забора, ₽</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>D212</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Клевер»</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>750</v>
-      </c>
-      <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>D006DKLC005</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Кольцо-печатка «Зеленый глаз»</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>3680</v>
+      </c>
+      <c r="I4" s="15" t="inlineStr"/>
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>D274</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Листики»</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>420</v>
-      </c>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>D006DKLC001-S</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Кольцо-печатка «Голубой глаз»</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>2760</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr"/>
+      <c r="J5" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>D249</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Капли»</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="n">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>D006DKLC001</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Кольцо-печатка «Голубой глаз»</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>2760</v>
+      </c>
+      <c r="I6" s="15" t="inlineStr"/>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>D006DKLC005-S</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Кольцо-печатка «Зеленый глаз»</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="F6" s="10" t="n">
-        <v>330</v>
-      </c>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>D354</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Ракушки»</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="17" t="n">
+        <v>2530</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr"/>
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>MSHK-039</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Найтли»</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>D006DKLC005-S</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Кольцо-печатка «Зеленый глаз»</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>1840</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr"/>
+      <c r="J8" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>MSH-074</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Эстелла»</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>270</v>
-      </c>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>D520</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Сережки «Ночное небо»</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>1840</v>
+      </c>
+      <c r="I9" s="15" t="inlineStr"/>
+      <c r="J9" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>D159</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Скарабеи»</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>240</v>
-      </c>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>D114DSMR034</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Моносережка «Перо»</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>1380</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr"/>
+      <c r="J10" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>MSHK-037</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Габриэль»</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>240</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>D518</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Сережки «Тропики»</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>1380</v>
+      </c>
+      <c r="I11" s="15" t="inlineStr"/>
+      <c r="J11" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>D531</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Доминика»</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>240</v>
-      </c>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>D519</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Сережки «Весенние тюльпаны»</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>1380</v>
+      </c>
+      <c r="I12" s="15" t="inlineStr"/>
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>MSHK-028</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Колье «Алма»</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>D006DKLC005-S</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Кольцо-печатка «Зеленый глаз»</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>1380</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr"/>
+      <c r="J13" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>D388</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Листва»</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="G14" s="8" t="inlineStr"/>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>D006DKLC005-S</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Кольцо-печатка «Зеленый глаз»</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="I14" s="15" t="inlineStr"/>
+      <c r="J14" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>D542</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Кольцо «Анемон»</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="G15" s="8" t="inlineStr"/>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>D006DKLC001</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Кольцо-печатка «Голубой глаз»</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>920</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr"/>
+      <c r="J15" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>D355</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Рыбки»</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="G16" s="8" t="inlineStr"/>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>D006DKLC003</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Кольцо-печатка «Карий глаз»</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>920</v>
+      </c>
+      <c r="I16" s="15" t="inlineStr"/>
+      <c r="J16" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>MSH-082</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Сабрина»</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="G17" s="8" t="inlineStr"/>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>D493</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Сережки «Глаза»</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>920</v>
+      </c>
+      <c r="I17" s="15" t="inlineStr"/>
+      <c r="J17" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>D512</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Афина»</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="G18" s="8" t="inlineStr"/>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>D202DSR069-S</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Сережки «Змеи»</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>920</v>
+      </c>
+      <c r="I18" s="15" t="inlineStr"/>
+      <c r="J18" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>MSHK-045</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Зои»</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="G19" s="8" t="inlineStr"/>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>D006DKLC001</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Кольцо-печатка «Голубой глаз»</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>920</v>
+      </c>
+      <c r="I19" s="15" t="inlineStr"/>
+      <c r="J19" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>D535</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Камилла»</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="G20" s="8" t="inlineStr"/>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>D200DSR050</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Сережки «Бантики»</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>920</v>
+      </c>
+      <c r="I20" s="15" t="inlineStr"/>
+      <c r="J20" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>MSH-073</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Матильда»</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="G21" s="8" t="inlineStr"/>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>D508-S</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Моносережка «Бабочка»</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>690</v>
+      </c>
+      <c r="I21" s="15" t="inlineStr"/>
+      <c r="J21" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>MSH-083</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Сережки «Сабрина»</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="G22" s="8" t="inlineStr"/>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>D202DSR133</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Сережки «Анемоны»</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>690</v>
+      </c>
+      <c r="I22" s="15" t="inlineStr"/>
+      <c r="J22" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>D529</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Кольцо «Ирис»</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="G23" s="8" t="inlineStr"/>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>D507-S</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Сережки ассиметричные «Змеи»</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>690</v>
+      </c>
+      <c r="I23" s="15" t="inlineStr"/>
+      <c r="J23" s="15" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -1963,32 +2175,42 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>D519</t>
+          <t>D212</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Весенние тюльпаны»</t>
+          <t>Сережки «Клевер»</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="G24" s="8" t="inlineStr"/>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>750</v>
+      </c>
+      <c r="I24" s="8" t="inlineStr"/>
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -1997,32 +2219,42 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>D236</t>
+          <t>D274</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Цикада»</t>
+          <t>Сережки «Листики»</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="G25" s="8" t="inlineStr"/>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>420</v>
+      </c>
+      <c r="I25" s="8" t="inlineStr"/>
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2031,32 +2263,42 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>MSH-007</t>
+          <t>D249</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Исидора»</t>
+          <t>Сережки «Капли»</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F26" s="10" t="n">
-        <v>180</v>
-      </c>
-      <c r="G26" s="8" t="inlineStr"/>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>330</v>
+      </c>
+      <c r="I26" s="8" t="inlineStr"/>
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2065,32 +2307,42 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>D364</t>
+          <t>D354</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Кэрри»</t>
+          <t>Сережки «Ракушки»</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F27" s="10" t="n">
-        <v>180</v>
-      </c>
-      <c r="G27" s="8" t="inlineStr"/>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="I27" s="8" t="inlineStr"/>
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2099,32 +2351,42 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>D528</t>
+          <t>MSHK-039</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Кольцо «Ирис»</t>
+          <t>Сережки «Найтли»</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F28" s="10" t="n">
-        <v>180</v>
-      </c>
-      <c r="G28" s="8" t="inlineStr"/>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="I28" s="8" t="inlineStr"/>
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2133,32 +2395,42 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>D495</t>
+          <t>MSH-074</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Кольцо «Роза»</t>
+          <t>Сережки «Эстелла»</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>180</v>
-      </c>
-      <c r="G29" s="8" t="inlineStr"/>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>270</v>
+      </c>
+      <c r="I29" s="8" t="inlineStr"/>
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2167,32 +2439,42 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>D513</t>
+          <t>D159</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Афина»</t>
+          <t>Сережки «Скарабеи»</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>180</v>
-      </c>
-      <c r="G30" s="8" t="inlineStr"/>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="I30" s="8" t="inlineStr"/>
+      <c r="J30" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2201,32 +2483,42 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>MSHK-055</t>
+          <t>MSHK-037</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Эмма»</t>
+          <t>Сережки «Габриэль»</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>180</v>
-      </c>
-      <c r="G31" s="8" t="inlineStr"/>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="I31" s="8" t="inlineStr"/>
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2235,32 +2527,42 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>D216</t>
+          <t>D531</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Колибри»</t>
+          <t>Сережки «Доминика»</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>150</v>
-      </c>
-      <c r="G32" s="8" t="inlineStr"/>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="I32" s="8" t="inlineStr"/>
+      <c r="J32" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2269,32 +2571,42 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>MSH-002</t>
+          <t>MSHK-028</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Египетские скарабеи»</t>
+          <t>Колье «Алма»</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
+          <t>Колье</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>42-47</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F33" s="10" t="n">
-        <v>150</v>
-      </c>
-      <c r="G33" s="8" t="inlineStr"/>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="I33" s="8" t="inlineStr"/>
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2303,32 +2615,42 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>D527</t>
+          <t>D388</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Кольцо «Ирис»</t>
+          <t>Сережки «Листва»</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F34" s="10" t="n">
-        <v>150</v>
-      </c>
-      <c r="G34" s="8" t="inlineStr"/>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="I34" s="8" t="inlineStr"/>
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2337,32 +2659,42 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>MSH-096</t>
+          <t>D542</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Валерия»</t>
+          <t>Кольцо «Анемон»</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>16-19</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F35" s="10" t="n">
-        <v>150</v>
-      </c>
-      <c r="G35" s="8" t="inlineStr"/>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="I35" s="8" t="inlineStr"/>
+      <c r="J35" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2371,32 +2703,42 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>MSH-078</t>
+          <t>D355</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Жанин»</t>
+          <t>Сережки «Рыбки»</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F36" s="10" t="n">
-        <v>150</v>
-      </c>
-      <c r="G36" s="8" t="inlineStr"/>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H36" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="I36" s="8" t="inlineStr"/>
+      <c r="J36" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2405,32 +2747,42 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>MSH-013</t>
+          <t>MSH-082</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Лучиана»</t>
+          <t>Сережки «Сабрина»</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>150</v>
-      </c>
-      <c r="G37" s="8" t="inlineStr"/>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H37" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="I37" s="8" t="inlineStr"/>
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2439,32 +2791,42 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>MSH-026</t>
+          <t>D512</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Алисия»</t>
+          <t>Сережки «Афина»</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>150</v>
-      </c>
-      <c r="G38" s="8" t="inlineStr"/>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="I38" s="8" t="inlineStr"/>
+      <c r="J38" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2473,32 +2835,42 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>D518</t>
+          <t>MSHK-045</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Тропики»</t>
+          <t>Сережки «Зои»</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>120</v>
-      </c>
-      <c r="G39" s="8" t="inlineStr"/>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="I39" s="8" t="inlineStr"/>
+      <c r="J39" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2507,32 +2879,42 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>D292</t>
+          <t>D535</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Винтаж»</t>
+          <t>Сережки «Камилла»</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>120</v>
-      </c>
-      <c r="G40" s="8" t="inlineStr"/>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="I40" s="8" t="inlineStr"/>
+      <c r="J40" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2541,32 +2923,42 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>D117</t>
+          <t>MSH-073</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Сережки ассиметричные «Змеи»</t>
+          <t>Сережки «Матильда»</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F41" s="10" t="n">
-        <v>120</v>
-      </c>
-      <c r="G41" s="8" t="inlineStr"/>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H41" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="I41" s="8" t="inlineStr"/>
+      <c r="J41" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2575,32 +2967,42 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>MSH-065</t>
+          <t>MSH-083</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Агнес»</t>
+          <t>Сережки «Сабрина»</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F42" s="10" t="n">
-        <v>120</v>
-      </c>
-      <c r="G42" s="8" t="inlineStr"/>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H42" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="I42" s="8" t="inlineStr"/>
+      <c r="J42" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2609,32 +3011,42 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>MSHK-029</t>
+          <t>D529</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Колье «Счастливое число 7»</t>
+          <t>Кольцо «Ирис»</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="G43" s="8" t="inlineStr"/>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="I43" s="8" t="inlineStr"/>
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2643,66 +3055,86 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>D360</t>
+          <t>D519</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Звездочки»</t>
+          <t>Сережки «Весенние тюльпаны»</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F44" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="G44" s="8" t="inlineStr"/>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="I44" s="8" t="inlineStr"/>
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>D507-S</t>
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>D236</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Сережки ассиметричные «Змеи»</t>
+          <t>Сережки «Цикада»</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="G45" s="8" t="inlineStr"/>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H45" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="I45" s="8" t="inlineStr"/>
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2711,32 +3143,42 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>D523</t>
+          <t>MSH-007</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Сережки «День и ночь»</t>
+          <t>Сережки «Исидора»</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="G46" s="8" t="inlineStr"/>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="I46" s="8" t="inlineStr"/>
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2745,32 +3187,42 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>D491</t>
+          <t>D364</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Катарина»</t>
+          <t>Сережки «Кэрри»</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F47" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="G47" s="8" t="inlineStr"/>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H47" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="I47" s="8" t="inlineStr"/>
+      <c r="J47" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2779,32 +3231,42 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>MSH-094</t>
+          <t>D528</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Сережки «Лора»</t>
+          <t>Кольцо «Ирис»</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="G48" s="8" t="inlineStr"/>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="I48" s="8" t="inlineStr"/>
+      <c r="J48" s="8" t="inlineStr">
         <is>
           <t>Запланировано</t>
         </is>
@@ -2813,757 +3275,2956 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
+          <t>D495</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Кольцо «Роза»</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="I49" s="8" t="inlineStr"/>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>D513</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Афина»</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H50" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="I50" s="8" t="inlineStr"/>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>MSHK-055</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Эмма»</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H51" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="I51" s="8" t="inlineStr"/>
+      <c r="J51" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>D216</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Колибри»</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="I52" s="8" t="inlineStr"/>
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>MSH-002</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Египетские скарабеи»</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="I53" s="8" t="inlineStr"/>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>D527</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Кольцо «Ирис»</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H54" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="I54" s="8" t="inlineStr"/>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>MSH-096</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Валерия»</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="I55" s="8" t="inlineStr"/>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>MSH-078</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Жанин»</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="I56" s="8" t="inlineStr"/>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>MSH-013</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Лучиана»</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="I57" s="8" t="inlineStr"/>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>MSH-026</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Алисия»</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H58" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="I58" s="8" t="inlineStr"/>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>D518</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Тропики»</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H59" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="I59" s="8" t="inlineStr"/>
+      <c r="J59" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>D292</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Винтаж»</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H60" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="I60" s="8" t="inlineStr"/>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>D117</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>Сережки ассиметричные «Змеи»</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H61" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="I61" s="8" t="inlineStr"/>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>MSH-065</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Агнес»</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H62" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="I62" s="8" t="inlineStr"/>
+      <c r="J62" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>MSHK-029</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>Колье «Счастливое число 7»</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Колье</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>40-45</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H63" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="I63" s="8" t="inlineStr"/>
+      <c r="J63" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>D360</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Звездочки»</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H64" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="I64" s="8" t="inlineStr"/>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>D507-S</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>Сережки ассиметричные «Змеи»</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="I65" s="8" t="inlineStr"/>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>D523</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «День и ночь»</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H66" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="I66" s="8" t="inlineStr"/>
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>D491</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Катарина»</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H67" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="I67" s="8" t="inlineStr"/>
+      <c r="J67" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>MSH-094</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>Сережки «Лора»</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H68" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="I68" s="8" t="inlineStr"/>
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
           <t>MSH-097</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>Сережки «Тайна сердца»</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
         <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="n">
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>Забрать</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F49" s="10" t="n">
+      <c r="H69" s="10" t="n">
         <v>90</v>
       </c>
-      <c r="G49" s="8" t="inlineStr"/>
-      <c r="H49" s="8" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="I69" s="8" t="inlineStr"/>
+      <c r="J69" s="8" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>MSHK-031</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>Колье «Наоми»</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>Колье</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>40-45</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H70" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="12" t="inlineStr"/>
+      <c r="J70" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
         <is>
           <t>MSHK-039</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B71" s="13" t="inlineStr">
         <is>
           <t>Сережки «Найтли»</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="G71" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F50" s="14" t="n">
+      <c r="H71" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G50" s="12" t="inlineStr"/>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="I71" s="12" t="inlineStr"/>
+      <c r="J71" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>MSHK-043</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>Браслет «Сальма»</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>Браслет</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>14-20</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H72" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="12" t="inlineStr"/>
+      <c r="J72" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>D523</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «День и ночь»</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H73" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="12" t="inlineStr"/>
+      <c r="J73" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>MSHK-055</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Эмма»</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H74" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="12" t="inlineStr"/>
+      <c r="J74" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>MSH-072</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B75" s="13" t="inlineStr">
         <is>
           <t>Сережки «Барбара»</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="G75" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F51" s="14" t="n">
+      <c r="H75" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G51" s="12" t="inlineStr"/>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="I75" s="12" t="inlineStr"/>
+      <c r="J75" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
         <is>
           <t>MSH-013</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>Сережки «Лучиана»</t>
         </is>
       </c>
-      <c r="C52" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="G76" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F52" s="14" t="n">
+      <c r="H76" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G52" s="12" t="inlineStr"/>
-      <c r="H52" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="12" t="inlineStr">
+      <c r="I76" s="12" t="inlineStr"/>
+      <c r="J76" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>MSHK-056</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Эмма»</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H77" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="12" t="inlineStr"/>
+      <c r="J77" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>MSH-026</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Алисия»</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H78" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="12" t="inlineStr"/>
+      <c r="J78" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
         <is>
           <t>MSH-073</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B79" s="13" t="inlineStr">
         <is>
           <t>Сережки «Матильда»</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="G79" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F53" s="14" t="n">
+      <c r="H79" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G53" s="12" t="inlineStr"/>
-      <c r="H53" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="I79" s="12" t="inlineStr"/>
+      <c r="J79" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
         <is>
           <t>MSH-065</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B80" s="13" t="inlineStr">
         <is>
           <t>Сережки «Агнес»</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="G80" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F54" s="14" t="n">
+      <c r="H80" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G54" s="12" t="inlineStr"/>
-      <c r="H54" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="I80" s="12" t="inlineStr"/>
+      <c r="J80" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
         <is>
           <t>MSH-025</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B81" s="13" t="inlineStr">
         <is>
           <t>Сережки «Лаура»</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F55" s="14" t="n">
+      <c r="H81" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G55" s="12" t="inlineStr"/>
-      <c r="H55" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="I81" s="12" t="inlineStr"/>
+      <c r="J81" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>MSHK-053</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Эстер»</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H82" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="12" t="inlineStr"/>
+      <c r="J82" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
         <is>
           <t>D175DSR035</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B83" s="13" t="inlineStr">
         <is>
           <t>Сережки «Клевер»</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E56" s="12" t="n">
+      <c r="G83" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F56" s="14" t="n">
+      <c r="H83" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G56" s="12" t="inlineStr"/>
-      <c r="H56" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="12" t="inlineStr">
+      <c r="I83" s="12" t="inlineStr"/>
+      <c r="J83" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
         <is>
           <t>MSH-012</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B84" s="13" t="inlineStr">
         <is>
           <t>Сережки «Лучиана»</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E57" s="12" t="n">
+      <c r="G84" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F57" s="14" t="n">
+      <c r="H84" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G57" s="12" t="inlineStr"/>
-      <c r="H57" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="I84" s="12" t="inlineStr"/>
+      <c r="J84" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>MSHK-057</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Черная луна»</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H85" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="12" t="inlineStr"/>
+      <c r="J85" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>D491</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Катарина»</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H86" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="12" t="inlineStr"/>
+      <c r="J86" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>MSH-095</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Роксана»</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H87" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="12" t="inlineStr"/>
+      <c r="J87" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>MSH-078</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Жанин»</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H88" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="12" t="inlineStr"/>
+      <c r="J88" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>MSHK-038</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Франсис»</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H89" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="12" t="inlineStr"/>
+      <c r="J89" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="inlineStr">
         <is>
           <t>D513</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B90" s="13" t="inlineStr">
         <is>
           <t>Сережки «Афина»</t>
         </is>
       </c>
-      <c r="C58" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D58" s="12" t="inlineStr">
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E58" s="12" t="n">
+      <c r="G90" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F58" s="14" t="n">
+      <c r="H90" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G58" s="12" t="inlineStr"/>
-      <c r="H58" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="I90" s="12" t="inlineStr"/>
+      <c r="J90" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>D531</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Доминика»</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H91" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="12" t="inlineStr"/>
+      <c r="J91" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
         <is>
           <t>D175DSR098</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B92" s="13" t="inlineStr">
         <is>
           <t>Сережки «Нежный клевер»</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E59" s="12" t="n">
+      <c r="G92" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F59" s="14" t="n">
+      <c r="H92" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G59" s="12" t="inlineStr"/>
-      <c r="H59" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="inlineStr">
+      <c r="I92" s="12" t="inlineStr"/>
+      <c r="J92" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
         <is>
           <t>MSHK-037</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B93" s="13" t="inlineStr">
         <is>
           <t>Сережки «Габриэль»</t>
         </is>
       </c>
-      <c r="C60" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E60" s="12" t="n">
+      <c r="G93" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F60" s="14" t="n">
+      <c r="H93" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G60" s="12" t="inlineStr"/>
-      <c r="H60" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+      <c r="I93" s="12" t="inlineStr"/>
+      <c r="J93" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>MSHK-045</t>
+        </is>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Зои»</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H94" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="12" t="inlineStr"/>
+      <c r="J94" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
         <is>
           <t>MSHK-036</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B95" s="13" t="inlineStr">
         <is>
           <t>Сережки «Сильвия»</t>
         </is>
       </c>
-      <c r="C61" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E61" s="12" t="n">
+      <c r="G95" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F61" s="14" t="n">
+      <c r="H95" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G61" s="12" t="inlineStr"/>
-      <c r="H61" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="I95" s="12" t="inlineStr"/>
+      <c r="J95" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>D155DKLC125</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>Кольцо «Джейн»</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H96" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="12" t="inlineStr"/>
+      <c r="J96" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>MSH-077</t>
+        </is>
+      </c>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Вирджиния»</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F97" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H97" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="12" t="inlineStr"/>
+      <c r="J97" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="inlineStr">
         <is>
           <t>MSH-074</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B98" s="13" t="inlineStr">
         <is>
           <t>Сережки «Эстелла»</t>
         </is>
       </c>
-      <c r="C62" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F98" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E62" s="12" t="n">
+      <c r="G98" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F62" s="14" t="n">
+      <c r="H98" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G62" s="12" t="inlineStr"/>
-      <c r="H62" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="I98" s="12" t="inlineStr"/>
+      <c r="J98" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>MSH-019</t>
+        </is>
+      </c>
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Флора»</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F99" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H99" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="12" t="inlineStr"/>
+      <c r="J99" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>DSR387</t>
+        </is>
+      </c>
+      <c r="B100" s="13" t="inlineStr">
+        <is>
+          <t>Колье «Листва»</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>Колье</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>36-45</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H100" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="12" t="inlineStr"/>
+      <c r="J100" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>D494</t>
+        </is>
+      </c>
+      <c r="B101" s="13" t="inlineStr">
+        <is>
+          <t>Кольцо «Роза»</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H101" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="12" t="inlineStr"/>
+      <c r="J101" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="inlineStr">
         <is>
           <t>MSH-070</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B102" s="13" t="inlineStr">
         <is>
           <t>Сережки «Марго»</t>
         </is>
       </c>
-      <c r="C63" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E63" s="12" t="n">
+      <c r="G102" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F63" s="14" t="n">
+      <c r="H102" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G63" s="12" t="inlineStr"/>
-      <c r="H63" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="I102" s="12" t="inlineStr"/>
+      <c r="J102" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
         <is>
           <t>D175DSR034</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="B103" s="13" t="inlineStr">
         <is>
           <t>Сережки «Клевер»</t>
         </is>
       </c>
-      <c r="C64" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E64" s="12" t="n">
+      <c r="G103" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F64" s="14" t="n">
+      <c r="H103" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G64" s="12" t="inlineStr"/>
-      <c r="H64" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="I103" s="12" t="inlineStr"/>
+      <c r="J103" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>D193DSR044</t>
+        </is>
+      </c>
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Ава»</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H104" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="12" t="inlineStr"/>
+      <c r="J104" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>MSHK-046</t>
+        </is>
+      </c>
+      <c r="B105" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Змея и месяц»</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H105" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="12" t="inlineStr"/>
+      <c r="J105" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>MSHK-050</t>
+        </is>
+      </c>
+      <c r="B106" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Френсис»</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H106" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="12" t="inlineStr"/>
+      <c r="J106" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
         <is>
           <t>MSH-014</t>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="B107" s="13" t="inlineStr">
         <is>
           <t>Сережки «Азалия»</t>
         </is>
       </c>
-      <c r="C65" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F107" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E65" s="12" t="n">
+      <c r="G107" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F65" s="14" t="n">
+      <c r="H107" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G65" s="12" t="inlineStr"/>
-      <c r="H65" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
+      <c r="I107" s="12" t="inlineStr"/>
+      <c r="J107" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="12" t="inlineStr">
         <is>
           <t>D193DSR047</t>
         </is>
       </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="B108" s="13" t="inlineStr">
         <is>
           <t>Сережки «Ника»</t>
         </is>
       </c>
-      <c r="C66" s="12" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="inlineStr">
         <is>
           <t>Распродать</t>
         </is>
       </c>
-      <c r="E66" s="12" t="n">
+      <c r="G108" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F66" s="14" t="n">
+      <c r="H108" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G66" s="12" t="inlineStr"/>
-      <c r="H66" s="12" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="15" t="inlineStr">
-        <is>
-          <t>D114DSMR034</t>
-        </is>
-      </c>
-      <c r="B67" s="16" t="inlineStr">
-        <is>
-          <t>Моносережка «Перо»</t>
-        </is>
-      </c>
-      <c r="C67" s="15" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D67" s="15" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E67" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="F67" s="17" t="n">
-        <v>1380</v>
-      </c>
-      <c r="G67" s="15" t="inlineStr"/>
-      <c r="H67" s="15" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="15" t="inlineStr">
-        <is>
-          <t>D493</t>
-        </is>
-      </c>
-      <c r="B68" s="16" t="inlineStr">
-        <is>
-          <t>Сережки «Глаза»</t>
-        </is>
-      </c>
-      <c r="C68" s="15" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D68" s="15" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E68" s="15" t="n">
+      <c r="I108" s="12" t="inlineStr"/>
+      <c r="J108" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>MSH-088</t>
+        </is>
+      </c>
+      <c r="B109" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Магдалина»</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G109" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F68" s="17" t="n">
-        <v>920</v>
-      </c>
-      <c r="G68" s="15" t="inlineStr"/>
-      <c r="H68" s="15" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="15" t="inlineStr">
-        <is>
-          <t>D202DSR069-S</t>
-        </is>
-      </c>
-      <c r="B69" s="16" t="inlineStr">
-        <is>
-          <t>Сережки «Змеи»</t>
-        </is>
-      </c>
-      <c r="C69" s="15" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D69" s="15" t="inlineStr">
-        <is>
-          <t>Забрать</t>
-        </is>
-      </c>
-      <c r="E69" s="15" t="n">
+      <c r="H109" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="12" t="inlineStr"/>
+      <c r="J109" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>D522</t>
+        </is>
+      </c>
+      <c r="B110" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Месяц и звезда»</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G110" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F69" s="17" t="n">
-        <v>920</v>
-      </c>
-      <c r="G69" s="15" t="inlineStr"/>
-      <c r="H69" s="15" t="inlineStr">
-        <is>
-          <t>Запланировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="18" t="inlineStr">
+      <c r="H110" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="12" t="inlineStr"/>
+      <c r="J110" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>D262DKLC007</t>
+        </is>
+      </c>
+      <c r="B111" s="13" t="inlineStr">
+        <is>
+          <t>Кольцо «Ника»</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F111" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H111" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="12" t="inlineStr"/>
+      <c r="J111" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>D509</t>
+        </is>
+      </c>
+      <c r="B112" s="13" t="inlineStr">
+        <is>
+          <t>Сережки «Алана»</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>Серьги</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H112" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="12" t="inlineStr"/>
+      <c r="J112" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>D184DKLE011</t>
+        </is>
+      </c>
+      <c r="B113" s="13" t="inlineStr">
+        <is>
+          <t>Колье «Синди»</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>Колье</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F113" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H113" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="12" t="inlineStr"/>
+      <c r="J113" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="12" t="inlineStr">
+        <is>
+          <t>D155DKLC125</t>
+        </is>
+      </c>
+      <c r="B114" s="13" t="inlineStr">
+        <is>
+          <t>Кольцо «Джейн»</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>Кольца</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="F114" s="12" t="inlineStr">
+        <is>
+          <t>Распродать</t>
+        </is>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H114" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="12" t="inlineStr"/>
+      <c r="J114" s="12" t="inlineStr">
+        <is>
+          <t>Запланировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="18" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B71" s="5" t="n"/>
-      <c r="C71" s="5" t="n"/>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="18">
-        <f>SUM(E4:E69)</f>
+      <c r="B116" s="5" t="n"/>
+      <c r="C116" s="5" t="n"/>
+      <c r="D116" s="5" t="n"/>
+      <c r="E116" s="5" t="n"/>
+      <c r="F116" s="5" t="n"/>
+      <c r="G116" s="18">
+        <f>SUM(G4:G114)</f>
         <v/>
       </c>
-      <c r="F71" s="19">
-        <f>SUM(F4:F69)</f>
+      <c r="H116" s="19">
+        <f>SUM(H4:H114)</f>
         <v/>
       </c>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>Ставки: WB 230 ₽/шт, Ozon 30 ₽/шт (товар возвращается для перепродажи). Распродажа/списание — забор 0 ₽.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Оранжевый — Ozon забрать (мёртвый неликвид) · Зелёный — WB распродать · Жёлтый — WB забрать (дорогой L1).</t>
+      <c r="I116" s="5" t="n"/>
+      <c r="J116" s="5" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Ставки: WB 230 ₽/шт, Ozon 30 ₽/шт (товар возвращается). Распродажа/списание — забор 0 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>🟡 WB забрать (дорогой L1, вещь дороже забора) · 🟠 Ozon забрать (30 ₽) · 🟢 WB распродать (забор дороже товара).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Критерий мёртвого: остаток ≥3 шт И заказы за 40 дней ≤1 (по каждой площадке отдельно). Ярлык FBS/FBO не учитывается — весь складской остаток из столбцов BM–BZ.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 D39 D40 D41 D42 D43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Забрать,Распродать,Списать"</formula1>
     </dataValidation>
-    <dataValidation sqref="H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 J102 J103 J104 J105 J106 J107 J108 J109 J110 J111 J112 J113 J114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Запланировано,В работе,Готово"</formula1>
     </dataValidation>
   </dataValidations>
